--- a/data/trans_dic/P26-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P26-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,65; 31,97</t>
+          <t>24,69; 31,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,28; 31,06</t>
+          <t>24,59; 31,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,1; 28,99</t>
+          <t>22,26; 29,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 12,55</t>
+          <t>6,25; 12,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,54; 41,39</t>
+          <t>33,79; 41,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,87; 41,79</t>
+          <t>33,78; 42,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,86; 30,76</t>
+          <t>23,85; 30,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,39; 11,29</t>
+          <t>7,47; 11,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,15; 35,6</t>
+          <t>30,15; 35,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,1; 35,42</t>
+          <t>30,07; 35,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,1; 28,92</t>
+          <t>24,0; 28,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 11,13</t>
+          <t>7,34; 11,07</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,83; 31,99</t>
+          <t>26,15; 32,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,49; 35,66</t>
+          <t>29,55; 35,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,05; 26,72</t>
+          <t>20,98; 26,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,48; 59,63</t>
+          <t>8,46; 68,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,34; 40,89</t>
+          <t>34,46; 41,11</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,91; 43,56</t>
+          <t>36,88; 43,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,69; 28,24</t>
+          <t>22,42; 28,02</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,48; 16,53</t>
+          <t>12,24; 16,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,72; 35,33</t>
+          <t>31,07; 35,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,13; 38,48</t>
+          <t>34,23; 38,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,49; 26,69</t>
+          <t>22,32; 26,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 52,29</t>
+          <t>11,3; 48,52</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,32; 33,6</t>
+          <t>25,87; 33,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,33; 36,6</t>
+          <t>29,39; 36,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,95; 31,79</t>
+          <t>24,6; 31,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 16,04</t>
+          <t>9,28; 15,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>32,04; 39,67</t>
+          <t>31,95; 39,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,51; 45,06</t>
+          <t>37,5; 45,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,26; 38,47</t>
+          <t>31,02; 38,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 17,15</t>
+          <t>6,32; 17,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,03; 35,47</t>
+          <t>30,25; 35,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,37; 40,01</t>
+          <t>34,66; 39,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,02; 33,97</t>
+          <t>28,77; 33,78</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,41</t>
+          <t>7,31; 15,21</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,14; 30,93</t>
+          <t>25,03; 30,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,74; 40,21</t>
+          <t>33,55; 40,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,42; 27,2</t>
+          <t>21,17; 27,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 18,59</t>
+          <t>12,71; 18,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,0; 40,46</t>
+          <t>33,95; 40,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 39,22</t>
+          <t>33,08; 39,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 24,7</t>
+          <t>18,94; 24,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 16,51</t>
+          <t>11,16; 16,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,37; 34,89</t>
+          <t>30,41; 35,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,3; 38,88</t>
+          <t>34,44; 38,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,08; 25,09</t>
+          <t>21,12; 25,01</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,67; 16,78</t>
+          <t>12,74; 16,77</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>26,86; 30,13</t>
+          <t>27,03; 30,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,4; 34,62</t>
+          <t>31,31; 34,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,62; 26,85</t>
+          <t>23,71; 26,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 38,5</t>
+          <t>11,2; 36,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,32; 38,83</t>
+          <t>35,37; 38,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,15; 40,41</t>
+          <t>36,9; 40,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,12; 28,2</t>
+          <t>25,04; 28,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,37; 14,3</t>
+          <t>10,25; 14,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,08</t>
+          <t>31,63; 34,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,64; 37,1</t>
+          <t>34,58; 37,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,86; 27,16</t>
+          <t>24,91; 27,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,95; 26,66</t>
+          <t>11,88; 26,28</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que tienen algún familiar que fuma habitualmente en casa</t>
+          <t>Población que tienen algún familiar que fuma habitualmente en casa (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>158443; 205476</t>
+          <t>158731; 204372</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>165327; 211502</t>
+          <t>167431; 213818</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135290; 177443</t>
+          <t>136252; 180164</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35297; 69823</t>
+          <t>34779; 70074</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>209414; 258429</t>
+          <t>210985; 257492</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>221377; 273089</t>
+          <t>220784; 275597</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>148948; 192042</t>
+          <t>148935; 192996</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>44574; 68075</t>
+          <t>45020; 68884</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>382079; 451124</t>
+          <t>382005; 448135</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>401689; 472679</t>
+          <t>401261; 472956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>297959; 357517</t>
+          <t>296716; 356875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86224; 128976</t>
+          <t>85028; 128349</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>234294; 290207</t>
+          <t>237214; 292762</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>289459; 349967</t>
+          <t>290020; 350639</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>203280; 257956</t>
+          <t>202544; 260171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94654; 665802</t>
+          <t>94488; 766248</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>305658; 363898</t>
+          <t>306667; 365848</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>366260; 432258</t>
+          <t>365995; 433832</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>222295; 276611</t>
+          <t>219661; 274480</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>109030; 144408</t>
+          <t>106922; 145416</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>552059; 635016</t>
+          <t>558370; 636309</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>673673; 759453</t>
+          <t>675680; 762153</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>437421; 519137</t>
+          <t>434046; 514071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>224605; 1040506</t>
+          <t>224843; 965604</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>167024; 213228</t>
+          <t>164188; 211138</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>210234; 262372</t>
+          <t>210668; 263289</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>180432; 229931</t>
+          <t>177946; 231022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>58225; 103614</t>
+          <t>59934; 101849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>199772; 247362</t>
+          <t>199176; 247224</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>274916; 330207</t>
+          <t>274806; 330977</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>229088; 281895</t>
+          <t>227311; 280135</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49529; 151427</t>
+          <t>55818; 154725</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>377814; 446201</t>
+          <t>380628; 447909</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>498267; 580004</t>
+          <t>502490; 576559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>422513; 494695</t>
+          <t>418854; 491852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>119820; 235636</t>
+          <t>111838; 232577</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>217999; 268244</t>
+          <t>217065; 268581</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>304029; 362357</t>
+          <t>302392; 361472</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>182105; 231270</t>
+          <t>179930; 232742</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108904; 158228</t>
+          <t>108245; 158555</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>324573; 386201</t>
+          <t>324036; 382133</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>326439; 385910</t>
+          <t>325478; 387762</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>182026; 233767</t>
+          <t>179274; 231191</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>111426; 166048</t>
+          <t>112244; 167338</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>553271; 635581</t>
+          <t>553961; 638652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>646710; 732970</t>
+          <t>649296; 732306</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>378739; 450729</t>
+          <t>379406; 449327</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>235349; 311630</t>
+          <t>236650; 311479</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>819766; 919521</t>
+          <t>824973; 926295</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1030129; 1135805</t>
+          <t>1027083; 1135492</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>744248; 846071</t>
+          <t>747042; 847666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>362671; 1220357</t>
+          <t>354939; 1164886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1092109; 1200621</t>
+          <t>1093745; 1202815</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1249274; 1358923</t>
+          <t>1240770; 1360887</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>824932; 925972</t>
+          <t>822229; 926247</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>348927; 481007</t>
+          <t>344940; 485998</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1943595; 2094258</t>
+          <t>1943490; 2096193</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2301312; 2464960</t>
+          <t>2297091; 2459735</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1599733; 1747684</t>
+          <t>1603052; 1748846</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>781055; 1741870</t>
+          <t>776418; 1717584</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P26-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P26-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>24,69; 31,79</t>
+          <t>24,7; 31,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,59; 31,4</t>
+          <t>24,43; 31,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,26; 29,44</t>
+          <t>21,88; 29,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,6</t>
+          <t>6,42; 11,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>33,79; 41,24</t>
+          <t>33,81; 41,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,78; 42,17</t>
+          <t>33,98; 41,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,85; 30,91</t>
+          <t>23,82; 30,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,47; 11,43</t>
+          <t>7,37; 11,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>30,15; 35,36</t>
+          <t>30,06; 35,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,07; 35,44</t>
+          <t>30,09; 35,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24,0; 28,86</t>
+          <t>24,05; 28,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,34; 11,07</t>
+          <t>7,43; 10,9</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 32,27</t>
+          <t>25,69; 31,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29,55; 35,73</t>
+          <t>29,98; 35,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,98; 26,95</t>
+          <t>20,97; 26,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 68,63</t>
+          <t>7,11; 12,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,46; 41,11</t>
+          <t>34,21; 40,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,88; 43,72</t>
+          <t>36,78; 43,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,42; 28,02</t>
+          <t>22,29; 28,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,65</t>
+          <t>12,07; 16,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,07; 35,41</t>
+          <t>30,92; 35,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 38,61</t>
+          <t>34,11; 38,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22,32; 26,43</t>
+          <t>22,53; 26,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 48,52</t>
+          <t>10,26; 13,34</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,87; 33,27</t>
+          <t>26,15; 33,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29,39; 36,73</t>
+          <t>29,41; 36,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,6; 31,94</t>
+          <t>24,78; 31,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,77</t>
+          <t>8,65; 14,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,95; 39,65</t>
+          <t>32,2; 39,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,5; 45,16</t>
+          <t>37,4; 45,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,02; 38,23</t>
+          <t>31,28; 38,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,32; 17,52</t>
+          <t>13,41; 18,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>30,25; 35,6</t>
+          <t>30,25; 35,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34,66; 39,77</t>
+          <t>34,53; 39,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28,77; 33,78</t>
+          <t>28,88; 33,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 15,21</t>
+          <t>11,86; 16,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,03; 30,97</t>
+          <t>25,08; 30,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33,55; 40,11</t>
+          <t>33,65; 40,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,17; 27,38</t>
+          <t>21,41; 27,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 18,62</t>
+          <t>13,04; 18,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,95; 40,03</t>
+          <t>33,93; 39,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,08; 39,4</t>
+          <t>33,09; 39,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 24,42</t>
+          <t>19,35; 25,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 16,64</t>
+          <t>12,86; 17,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 35,06</t>
+          <t>30,64; 34,81</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34,44; 38,84</t>
+          <t>34,5; 39,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,12; 25,01</t>
+          <t>21,2; 25,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,74; 16,77</t>
+          <t>13,41; 16,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>12,62%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>27,03; 30,35</t>
+          <t>26,83; 30,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,31; 34,61</t>
+          <t>31,09; 34,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,71; 26,9</t>
+          <t>23,72; 26,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11,2; 36,75</t>
+          <t>10,21; 12,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,37; 38,9</t>
+          <t>35,5; 38,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,9; 40,47</t>
+          <t>36,99; 40,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,04; 28,21</t>
+          <t>25,24; 28,25</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 14,44</t>
+          <t>12,6; 14,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,63; 34,12</t>
+          <t>31,74; 34,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34,58; 37,03</t>
+          <t>34,57; 37,03</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24,91; 27,18</t>
+          <t>24,93; 27,11</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,88; 26,28</t>
+          <t>11,78; 13,51</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48772</t>
+          <t>52619</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>55429</t>
+          <t>60246</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>104201</t>
+          <t>112865</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>158731; 204372</t>
+          <t>158803; 205535</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>167431; 213818</t>
+          <t>166367; 212006</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136252; 180164</t>
+          <t>133940; 179741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34779; 70074</t>
+          <t>38730; 71641</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>210985; 257492</t>
+          <t>211108; 258382</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>220784; 275597</t>
+          <t>222102; 273179</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>148935; 192996</t>
+          <t>148719; 190936</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45020; 68884</t>
+          <t>48264; 74422</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>382005; 448135</t>
+          <t>380858; 447912</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>401261; 472956</t>
+          <t>401608; 469326</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>296716; 356875</t>
+          <t>297339; 355395</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85028; 128349</t>
+          <t>93403; 137091</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>325723</t>
+          <t>89121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>125182</t>
+          <t>136915</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>450905</t>
+          <t>226036</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>237214; 292762</t>
+          <t>233047; 289451</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>290020; 350639</t>
+          <t>294246; 352955</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>202544; 260171</t>
+          <t>202489; 256888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94488; 766248</t>
+          <t>68133; 115819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>306667; 365848</t>
+          <t>304451; 363777</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>365995; 433832</t>
+          <t>365016; 431063</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>219661; 274480</t>
+          <t>218344; 275788</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106922; 145416</t>
+          <t>118112; 161855</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>558370; 636309</t>
+          <t>555734; 636734</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>675680; 762153</t>
+          <t>673286; 764530</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>434046; 514071</t>
+          <t>438240; 517468</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>224843; 965604</t>
+          <t>198751; 258507</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78356</t>
+          <t>83578</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>120395</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>188627</t>
+          <t>203973</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>164188; 211138</t>
+          <t>165970; 210369</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>210668; 263289</t>
+          <t>210800; 262256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>177946; 231022</t>
+          <t>179210; 226418</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59934; 101849</t>
+          <t>62956; 108249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>199176; 247224</t>
+          <t>200741; 249209</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>274806; 330977</t>
+          <t>274070; 329866</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>227311; 280135</t>
+          <t>229250; 282536</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55818; 154725</t>
+          <t>101210; 140589</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>380628; 447909</t>
+          <t>380563; 450220</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>502490; 576559</t>
+          <t>500566; 573635</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>418854; 491852</t>
+          <t>420582; 493234</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>111838; 232577</t>
+          <t>175779; 240780</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133409</t>
+          <t>141070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>142509</t>
+          <t>150024</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>275917</t>
+          <t>291094</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>217065; 268581</t>
+          <t>217517; 265017</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>302392; 361472</t>
+          <t>303263; 364787</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>179930; 232742</t>
+          <t>182016; 230433</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>108245; 158555</t>
+          <t>118582; 168277</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>324036; 382133</t>
+          <t>323832; 380765</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>325478; 387762</t>
+          <t>325655; 388454</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>179274; 231191</t>
+          <t>183162; 236763</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>112244; 167338</t>
+          <t>131428; 173838</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>553961; 638652</t>
+          <t>558138; 634177</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>649296; 732306</t>
+          <t>650444; 736165</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>379406; 449327</t>
+          <t>380882; 454743</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>236650; 311479</t>
+          <t>259033; 325394</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>586260</t>
+          <t>366387</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>433391</t>
+          <t>467580</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1019650</t>
+          <t>833968</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>824973; 926295</t>
+          <t>818869; 923660</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1027083; 1135492</t>
+          <t>1019908; 1131297</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>747042; 847666</t>
+          <t>747300; 845332</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>354939; 1164886</t>
+          <t>326728; 413423</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1093745; 1202815</t>
+          <t>1097897; 1201372</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1240770; 1360887</t>
+          <t>1243776; 1360681</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>822229; 926247</t>
+          <t>828639; 927472</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>344940; 485998</t>
+          <t>429704; 505219</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1943490; 2096193</t>
+          <t>1949927; 2091256</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2297091; 2459735</t>
+          <t>2296675; 2459791</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1603052; 1748846</t>
+          <t>1604204; 1744154</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>776418; 1717584</t>
+          <t>778596; 892654</t>
         </is>
       </c>
     </row>
